--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_maule.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:28</t>
+    <t xml:space="preserve">2026-09-24 01:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -739,7 +739,7 @@
         <v>0.2</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.19</v>
@@ -759,10 +759,10 @@
         <v>30</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>-0.12</v>
@@ -785,7 +785,7 @@
         <v>0.16</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>-0.14</v>
@@ -799,19 +799,19 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="14">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_maule.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:18</t>
+    <t xml:space="preserve">2026-10-01 23:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_maule.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:17</t>
+    <t xml:space="preserve">2026-10-05 19:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
